--- a/111/111_111/006_AES3/条件输入数据表.xlsx
+++ b/111/111_111/006_AES3/条件输入数据表.xlsx
@@ -1169,12 +1169,24 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>介质特性（毒性危害程度）</t>
-        </is>
-      </c>
-      <c r="C3" s="33" t="inlineStr"/>
-      <c r="D3" s="33" t="inlineStr"/>
-      <c r="E3" s="17" t="inlineStr"/>
+          <t>设计压力*</t>
+        </is>
+      </c>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
           <t>设计压力*</t>
@@ -1198,12 +1210,24 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>介质特性（爆炸危险程度）</t>
-        </is>
-      </c>
-      <c r="C4" s="33" t="inlineStr"/>
-      <c r="D4" s="33" t="inlineStr"/>
-      <c r="E4" s="17" t="inlineStr"/>
+          <t>进、出口压力差*</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
           <t>设计温度（最高）*</t>
@@ -1227,12 +1251,24 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>介质特性（是否液化气体）</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr"/>
-      <c r="D5" s="33" t="inlineStr"/>
-      <c r="E5" s="17" t="inlineStr"/>
+          <t>设计温度（最高）*</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>工作压力</t>
@@ -1256,16 +1292,24 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>工作压力</t>
+          <t>沿长度平均的换热管金属温度*</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>MPa</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
           <t>工作温度（入口）</t>
@@ -1289,16 +1333,24 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>设计压力*</t>
+          <t>沿长度平均的壳程圆筒金属温度*</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>MPa</t>
-        </is>
-      </c>
-      <c r="D7" s="33" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>工作温度（出口）</t>
@@ -1322,16 +1374,24 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>最高允许工作压力</t>
+          <t>腐蚀裕量*</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
-          <t>MPa</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>最高允许工作压力</t>
@@ -1355,16 +1415,20 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>管板设计压差</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="inlineStr">
-        <is>
-          <t>MPa</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
+          <t>焊接接头系数*</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr"/>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="28" t="inlineStr">
@@ -1374,22 +1438,18 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>进、出口压力差*</t>
-        </is>
-      </c>
-      <c r="C10" s="33" t="inlineStr">
-        <is>
-          <t>MPa</t>
-        </is>
-      </c>
+          <t>耐压试验类型*</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr"/>
       <c r="D10" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>液压试验</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>液压试验</t>
         </is>
       </c>
     </row>
@@ -1401,14 +1461,10 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>设计温度（最高）*</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="inlineStr">
-        <is>
-          <t>℃</t>
-        </is>
-      </c>
+          <t>介质特性（毒性危害程度）</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr"/>
       <c r="D11" s="33" t="inlineStr"/>
       <c r="E11" s="17" t="inlineStr"/>
     </row>
@@ -1420,14 +1476,10 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>工作温度（入口）</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="inlineStr">
-        <is>
-          <t>℃</t>
-        </is>
-      </c>
+          <t>介质特性（爆炸危险程度）</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr"/>
       <c r="D12" s="33" t="inlineStr"/>
       <c r="E12" s="17" t="inlineStr"/>
     </row>
@@ -1439,14 +1491,10 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>工作温度（出口）</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>℃</t>
-        </is>
-      </c>
+          <t>介质特性（是否液化气体）</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr"/>
       <c r="D13" s="33" t="inlineStr"/>
       <c r="E13" s="17" t="inlineStr"/>
     </row>
@@ -1458,12 +1506,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>最低设计温度</t>
+          <t>工作压力</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr"/>
@@ -1477,19 +1525,15 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>沿长度平均的换热管金属温度*</t>
+          <t>最高允许工作压力</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1500,20 +1544,16 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>沿长度平均的壳程圆筒金属温度*</t>
+          <t>管板设计压差</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr"/>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="28" t="inlineStr">
@@ -1523,12 +1563,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>腐蚀裕量*</t>
+          <t>工作温度（入口）</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr"/>
@@ -1542,20 +1582,16 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>焊接接头系数*</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="inlineStr"/>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>工作温度（出口）</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr"/>
+      <c r="E18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="28" t="inlineStr">
@@ -1565,12 +1601,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>液柱静压力</t>
+          <t>最低设计温度</t>
         </is>
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="D19" s="33" t="inlineStr"/>
@@ -1584,10 +1620,14 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>介质（组分）</t>
-        </is>
-      </c>
-      <c r="C20" s="33" t="inlineStr"/>
+          <t>液柱静压力</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
       <c r="D20" s="33" t="inlineStr"/>
       <c r="E20" s="17" t="inlineStr"/>
     </row>
@@ -1599,7 +1639,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>介质（相态）</t>
+          <t>介质（组分）</t>
         </is>
       </c>
       <c r="C21" s="33" t="inlineStr"/>
@@ -1614,14 +1654,10 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>介质密度</t>
-        </is>
-      </c>
-      <c r="C22" s="33" t="inlineStr">
-        <is>
-          <t>kg/m³</t>
-        </is>
-      </c>
+          <t>介质（相态）</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr"/>
       <c r="D22" s="33" t="inlineStr"/>
       <c r="E22" s="17" t="inlineStr"/>
     </row>
@@ -1633,12 +1669,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>介质入口流速</t>
+          <t>介质密度</t>
         </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>kg/m³</t>
         </is>
       </c>
       <c r="D23" s="33" t="inlineStr"/>
@@ -1652,20 +1688,16 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>超压泄放装置</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="inlineStr"/>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>工艺系统考虑</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>工艺系统考虑</t>
-        </is>
-      </c>
+          <t>介质入口流速</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
@@ -1675,18 +1707,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>耐压试验类型*</t>
+          <t>超压泄放装置</t>
         </is>
       </c>
       <c r="C25" s="33" t="inlineStr"/>
       <c r="D25" s="33" t="inlineStr">
         <is>
-          <t>液压试验</t>
+          <t>工艺系统考虑</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>液压试验</t>
+          <t>工艺系统考虑</t>
         </is>
       </c>
     </row>
@@ -1908,9 +1940,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1970,7 +2002,7 @@
       <c r="C2" s="35" t="inlineStr"/>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
